--- a/regions/HS_071/HS_071.xlsx
+++ b/regions/HS_071/HS_071.xlsx
@@ -435,240 +435,265 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:sheetPr>
-    <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
-    <ns0:pageSetUpPr fitToPage="1"/>
-  </ns0:sheetPr>
-  <ns0:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <ns0:cols>
-    <ns0:col width="34" customWidth="1" min="1" max="1"/>
-    <ns0:col width="110" customWidth="1" min="2" max="2"/>
-    <ns0:col width="23" customWidth="1" min="3" max="3"/>
-    <ns0:col width="23" customWidth="1" min="4" max="4"/>
-    <ns0:col width="23" customWidth="1" min="5" max="5"/>
-    <ns0:col width="23" customWidth="1" min="6" max="6"/>
-    <ns0:col width="23" customWidth="1" min="7" max="7"/>
-    <ns0:col width="23" customWidth="1" min="8" max="8"/>
-  </ns0:cols>
-  <ns0:sheetData>
-    <ns0:row r="1">
-      <ns0:c r="A1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>@table</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Settings</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="2">
-      <ns0:c r="A2" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>field</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B2" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>value</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="3" ht="24" customHeight="1">
-      <ns0:c r="A3" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>unit_id</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B3" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>HS_071</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="4" ht="24" customHeight="1">
-      <ns0:c r="A4" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>region_name</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B4" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Pacific, Western Central</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="5" ht="24" customHeight="1">
-      <ns0:c r="A5" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>region_type</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B5" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>High Seas</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="6">
-      <ns0:c r="A6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>selected_model_id</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="7">
-      <ns0:c r="A7" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>selection_rationale</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="8">
-      <ns0:c r="A8" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>model_path</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="9">
-      <ns0:c r="A9" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>results_model_id</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="10">
-      <ns0:c r="A10" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>results_model_sha256</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="11" ht="24" customHeight="1">
-      <ns0:c r="A11" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>selected_paper_ids</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B11" s="2" t="inlineStr"/>
-    </ns0:row>
-    <ns0:row r="12" ht="24" customHeight="1">
-      <ns0:c r="A12" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>production_eligible</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B12" t="b">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="13" ht="24" customHeight="1">
-      <ns0:c r="A13" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>catch_basis</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B13" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>landings</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="14" ht="24" customHeight="1">
-      <ns0:c r="A14" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>transfer_efficiency</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B14" s="3" t="n">
-        <ns0:v>0.1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="15" ht="24" customHeight="1">
-      <ns0:c r="A15" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>taxon_detail_year</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B15" s="3" t="n">
-        <ns0:v>2019</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="16" ht="24" customHeight="1">
-      <ns0:c r="A16" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>source_note</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B16" s="2" t="inlineStr"/>
-    </ns0:row>
-    <ns0:row r="17" ht="24" customHeight="1">
-      <ns0:c r="A17" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>calculation_status</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B17" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>migrated saved results; unavailable methods retained</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="18" ht="24" customHeight="1">
-      <ns0:c r="A18" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>source_region_workbook</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B18" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>original_research_archive/legacy/data/HS_071/HS_071.xlsx</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="19" ht="24" customHeight="1">
-      <ns0:c r="A19" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>npp_policy</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B19" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Annual observed support; unsupported years stay blank; no earliest-year proxy by default</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="20" ht="24" customHeight="1">
-      <ns0:c r="A20" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>calculation_input_sha256</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B20" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>461b7510bab74354ea51b9d91eb073a7ccb5e5355c4a34c898cda8790c97effb</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="21" ht="24" customHeight="1">
-      <ns0:c r="A21" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>calculation_result_sha256</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B21" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>6b659df12e751fb77c440ef1a91dd23c33934a08de4cef2937e2ce38b66bc45c</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="22"/>
-  </ns0:sheetData>
-  <ns0:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</ns0:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>unit_id</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>HS_071</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>region_name</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Pacific, Western Central</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>region_type</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>High Seas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>selected_model_id</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>941_20070101_WCPO_Warm_Pool_Option1_(mixed_periods)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="128" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>selection_rationale</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>USER SELECTED 2026-09-28: WCP-2007 option 1 (D_fixed_M0) for HS_071, EEZ_941 and EEZ_598. Explicit experimental variant preserves juvenile other-mortality flows and changes Small BET P/B to 1.4129713563375232, EE to 0.7898725981469387; Small YFT P/B to 2.5304972811160384, EE to 0.8816702937266387. GE, TE and With Egestion all WARN; PP-budget checks OK, but strict mass balance remains false (adult BET residual 0.727940%). This is an adopted surrogate, not an author-confirmed correction or a region-specific native EwE model. Original source remains preserved. Griffiths 2019 source and pooled variant are retained for later investigation of failures, not selected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>model_path</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>models/941_20070101_WCPO_Warm_Pool_Option1_(mixed_periods)/941_20070101_WCPO_Warm_Pool_Option1_(mixed_periods).json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>results_model_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>results_model_sha256</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>selected_paper_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>production_eligible</t>
+        </is>
+      </c>
+      <c r="B12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>catch_basis</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>landings</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>transfer_efficiency</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>taxon_detail_year</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>source_note</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>calculation_status</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>selected; SPPR, matching and model PPR not yet calculated</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>source_region_workbook</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>original_research_archive/legacy/data/HS_071/HS_071.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>npp_policy</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Annual observed support; unsupported years stay blank; no earliest-year proxy by default</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>calculation_input_sha256</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>461b7510bab74354ea51b9d91eb073a7ccb5e5355c4a34c898cda8790c97effb</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>calculation_result_sha256</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>6b659df12e751fb77c440ef1a91dd23c33934a08de4cef2937e2ce38b66bc45c</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="96" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>griffiths_later_investigation</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>USER REQUEST 2026-09-28: retain Griffiths et al. (2019) for later investigation across HS_071, EEZ_941 and EEZ_598. Understand why it fails before considering adoption. Original 46-group extraction is blocked by unknown two-pool routing. The authorized 45-group pooled experiment loads but GE, TE and With Egestion all FAIL. Investigate the Pomfret production/predation inconsistency, 22 printed catch-total versus fleet-sum conflicts, and routing/fishery-return and loader effects separately. No further parameter repair is authorized by this note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18476,7 +18501,6 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
           <t>all</t>
@@ -18719,7 +18743,6 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
           <t>all</t>
@@ -18962,7 +18985,6 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
           <t>all</t>
@@ -19205,7 +19227,6 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
           <t>all</t>
@@ -19238,7 +19259,6 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
           <t>all</t>
@@ -19271,7 +19291,6 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
           <t>all</t>
@@ -19514,7 +19533,6 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
           <t>all</t>
@@ -19757,7 +19775,6 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
           <t>all</t>
@@ -20000,7 +20017,6 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
           <t>all</t>
@@ -20243,7 +20259,6 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
           <t>all</t>
@@ -20486,7 +20501,6 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
           <t>all</t>
@@ -20729,7 +20743,6 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
           <t>all</t>
@@ -20972,7 +20985,6 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
           <t>all</t>
@@ -21215,7 +21227,6 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
           <t>all</t>
@@ -21458,7 +21469,6 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
           <t>all</t>
@@ -21491,7 +21501,6 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
           <t>all</t>
@@ -21524,7 +21533,6 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
           <t>all</t>
@@ -21767,7 +21775,6 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
           <t>all</t>
@@ -22010,7 +22017,6 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
           <t>all</t>
@@ -22253,7 +22259,6 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
           <t>all</t>
@@ -22496,7 +22501,6 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
           <t>all</t>
@@ -22739,7 +22743,6 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
           <t>all</t>
@@ -22982,7 +22985,6 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
           <t>all</t>
@@ -23225,7 +23227,6 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
           <t>all</t>
@@ -23468,7 +23469,6 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
           <t>all</t>
@@ -23711,7 +23711,6 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
           <t>all</t>
@@ -23744,7 +23743,6 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
           <t>all</t>
@@ -23777,7 +23775,6 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
           <t>all</t>
@@ -24020,7 +24017,6 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
           <t>all</t>
@@ -24263,7 +24259,6 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
           <t>all</t>
@@ -24506,7 +24501,6 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
           <t>all</t>
@@ -24749,7 +24743,6 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
           <t>all</t>
@@ -24992,7 +24985,6 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
           <t>all</t>
@@ -29325,7 +29317,6 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>all</t>
@@ -29419,7 +29410,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>all</t>
@@ -29498,7 +29488,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>all</t>
@@ -29577,7 +29566,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>all</t>
@@ -29656,7 +29644,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>all</t>
@@ -29735,7 +29722,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>all</t>
@@ -29829,7 +29815,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>all</t>
@@ -29923,7 +29908,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>all</t>
@@ -30002,7 +29986,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>all</t>
@@ -30081,7 +30064,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>all</t>
@@ -30160,7 +30142,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>all</t>
@@ -30239,7 +30220,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>all</t>
@@ -30333,7 +30313,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>all</t>
@@ -30427,7 +30406,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>all</t>
@@ -30506,7 +30484,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>all</t>
@@ -30585,7 +30562,6 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>all</t>
@@ -30664,7 +30640,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>all</t>
@@ -30743,7 +30718,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>all</t>
@@ -30837,7 +30811,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>all</t>
@@ -30931,7 +30904,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>all</t>
@@ -31010,7 +30982,6 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>all</t>
@@ -31089,7 +31060,6 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>all</t>
@@ -31168,7 +31138,6 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
           <t>all</t>
@@ -31247,7 +31216,6 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
           <t>all</t>
@@ -31341,7 +31309,6 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
           <t>all</t>
@@ -31435,7 +31402,6 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
           <t>all</t>
@@ -31514,7 +31480,6 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
           <t>all</t>
@@ -31593,7 +31558,6 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
           <t>all</t>
@@ -31672,7 +31636,6 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
           <t>all</t>
@@ -31751,7 +31714,6 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
           <t>all</t>
@@ -31845,7 +31807,6 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
           <t>all</t>
@@ -31939,7 +31900,6 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
           <t>all</t>
@@ -32018,7 +31978,6 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
           <t>all</t>
@@ -32097,7 +32056,6 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
           <t>all</t>
@@ -32176,7 +32134,6 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
           <t>all</t>
@@ -32255,7 +32212,6 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
           <t>all</t>
@@ -32349,7 +32305,6 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
           <t>all</t>
@@ -32443,7 +32398,6 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
           <t>all</t>
@@ -32522,7 +32476,6 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
           <t>all</t>
@@ -32601,7 +32554,6 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
           <t>all</t>
@@ -32680,7 +32632,6 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
           <t>all</t>
@@ -32759,7 +32710,6 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
           <t>all</t>
@@ -32853,7 +32803,6 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
           <t>all</t>
@@ -32947,7 +32896,6 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
           <t>all</t>
@@ -33026,7 +32974,6 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
           <t>all</t>
@@ -33105,7 +33052,6 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
           <t>all</t>
@@ -33184,7 +33130,6 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
           <t>all</t>
@@ -33263,7 +33208,6 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
           <t>all</t>
@@ -33357,7 +33301,6 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
           <t>all</t>
@@ -33451,7 +33394,6 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
           <t>all</t>
@@ -33530,7 +33472,6 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
           <t>all</t>
@@ -33609,7 +33550,6 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
           <t>all</t>
@@ -33688,7 +33628,6 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
           <t>all</t>
@@ -33767,7 +33706,6 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
           <t>all</t>
